--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.0%</t>
+          <t>-610.1%</t>
         </is>
       </c>
     </row>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.484112393519346</v>
+        <v>-4.48541628038723</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9653340304699813</v>
+        <v>0.9648124757228276</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.8067838801303926</v>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-720.6%</t>
+          <t>-703.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-57.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.7%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.1%</t>
+          <t>-591.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-288.6%</t>
+          <t>-281.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-112.7%</t>
+          <t>-64.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.7%</t>
+          <t>-272.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-327.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.9%</t>
+          <t>-160.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-304.7%</t>
+          <t>-287.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-197.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-218.5%</t>
+          <t>-208.2%</t>
         </is>
       </c>
     </row>
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.234466960757366</v>
+        <v>-1.06255252149029</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.622937241334336</v>
+        <v>2.691703017041166</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9003695915878102</v>
+        <v>1.072284030854885</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.657302204903716</v>
+        <v>3.760450868463961</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.456088894315483</v>
+        <v>-1.284174455048408</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.53415468451001</v>
+        <v>2.602920460216841</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>1.034757897167516</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.737801404850461</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.66409295266856</v>
+        <v>-1.492178513401485</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.455845205722705</v>
+        <v>2.524610981429535</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>1.034757897167516</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.742693549404386</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.875505373556535</v>
+        <v>-1.70359093428946</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.366361693705503</v>
+        <v>2.435127469412333</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.8233454762795409</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.610927553209589</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.214663751145058</v>
+        <v>-2.042749311877983</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.223782641976543</v>
+        <v>2.292548417683373</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.4841870986910188</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.400516825962925</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.542680972872537</v>
+        <v>-2.370766533605462</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.11291404302432</v>
+        <v>2.18167981873115</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>0.1561698769635397</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.224044782665206</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.036005844407715</v>
+        <v>-2.86409140514064</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.923682844818817</v>
+        <v>1.992448620525647</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>0.05118376272392094</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.169151864530003</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.528390872431812</v>
+        <v>-3.356476433164737</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.727835225652911</v>
+        <v>1.796601001359741</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.4412012653001758</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.874827239759278</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.913571263361884</v>
+        <v>-3.741656824094809</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.572305608093745</v>
+        <v>1.641071383800575</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.4412012653001758</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.873369778572141</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.257254036588547</v>
+        <v>-4.085339597321472</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.436601622257696</v>
+        <v>1.505367397964526</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.5491073173273939</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.810395270810426</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.614904386826895</v>
+        <v>-4.44298994755982</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.289647540818615</v>
+        <v>1.358413316525445</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-0.9067576675657421</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.591911119323675</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.924138489822946</v>
+        <v>-4.752224050555871</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.167726826320454</v>
+        <v>1.236492602027284</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-0.9067576675657421</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.593684046023935</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.355944282972733</v>
+        <v>-5.184029843705658</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9813373965279433</v>
+        <v>1.050103172234774</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.043175164007009</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.498166435626579</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.590638277105286</v>
+        <v>-5.41872383783821</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8757445738770131</v>
+        <v>0.9445103495838429</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.036838896777754</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.490252970966222</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.926300924335738</v>
+        <v>-5.754386485068663</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7400601066407972</v>
+        <v>0.8088258823476271</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.036838896777754</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.488833562622188</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.289927169236051</v>
+        <v>-6.118012729968976</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6010971689149134</v>
+        <v>0.6698629446217432</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.13506053364488</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.436388140736154</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.655054551874798</v>
+        <v>-6.483140112607723</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.454300730865246</v>
+        <v>0.5230665065720763</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.431371317943892</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.257856185162578</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.063643329055477</v>
+        <v>-6.891728889788402</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2896267640077337</v>
+        <v>0.3583925397145635</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>2.01146446286893</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.476625813196571</v>
+        <v>-7.304711373929496</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1196192028227565</v>
+        <v>0.1883849785295868</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>2.006649895340391</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.893017687483568</v>
+        <v>-7.721103248216493</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.04894349628316519</v>
+        <v>0.0198222794236651</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>2.004643945949268</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.269694698013412</v>
+        <v>-8.097780258746337</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1893556098264235</v>
+        <v>-0.1205898341195932</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>2.014902636617947</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.615569519998221</v>
+        <v>-8.443655080731146</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3316059734746521</v>
+        <v>-0.2628401977678219</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>2.011002201763642</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.777711790461314</v>
+        <v>-8.605797351194239</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3980579616048883</v>
+        <v>-0.329292185898058</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.83996009512457</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>2.009407121818643</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.074373132271512</v>
+        <v>-8.902458693004437</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5129435223997594</v>
+        <v>-0.4441777466929291</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-1.908703230858449</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.971940216307524</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.507722240381748</v>
+        <v>-9.335807801114672</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6903094701782564</v>
+        <v>-0.6215436944714265</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-1.908703230858449</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.967913911773121</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.890723629124379</v>
+        <v>-9.718809189857303</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8436121269968933</v>
+        <v>-0.774846351290063</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-1.908703230858449</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.967811810451537</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.0481225093375</v>
+        <v>-9.876208070070424</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9040001631107111</v>
+        <v>-0.8352343874038812</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.06610211107157</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.875943998295094</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4076528318415</v>
+        <v>-10.23573839257443</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.042461988814262</v>
+        <v>-0.9736962131074316</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.06610211107157</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.881294301593144</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.73405286050651</v>
+        <v>-10.56213842123944</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.165105980323089</v>
+        <v>-1.096340204616259</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.392502139736583</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.693370304351314</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.95320182858071</v>
+        <v>-10.78128738931364</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.249723816930999</v>
+        <v>-1.18095804122417</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.61165110781078</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.564922674128564</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9495109036243</v>
+        <v>-10.77759646435723</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.248247446948435</v>
+        <v>-1.179481671241605</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.61165110781078</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.564922674128564</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.15376907895416</v>
+        <v>-10.98185463968709</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.324437519961738</v>
+        <v>-1.255671744254908</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.739290052424769</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.493852504478814</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.37180685058534</v>
+        <v>-11.19989241131827</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.407170074129774</v>
+        <v>-1.338404298422943</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-2.914060820520668</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.39347259810571</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.29833701891789</v>
+        <v>-11.12642257965082</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.362410439969373</v>
+        <v>-1.293644664262542</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-2.84059098885322</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.4529261985996</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.47346143630444</v>
+        <v>-11.30154699703736</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.417904986176473</v>
+        <v>-1.349139210469643</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.015715406239764</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.362406768915191</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.70791353031893</v>
+        <v>-11.53599909105185</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.518904988683865</v>
+        <v>-1.450139212977035</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.015715406239764</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.355187604013595</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.99571737485616</v>
+        <v>-11.82380293558909</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.640698717272736</v>
+        <v>-1.571932941565907</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.303519250777002</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.175833106517276</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.22554182201999</v>
+        <v>-12.05362738275291</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.731512706299711</v>
+        <v>-1.66274693059288</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.466166787847162</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>1.079360374113736</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.45757074175625</v>
+        <v>-12.28565630248918</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.821630545565101</v>
+        <v>-1.752864769858271</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.528179485035586</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>1.044846484429796</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.40555522778744</v>
+        <v>-12.23364078852036</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.796834004291174</v>
+        <v>-1.728068228584345</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.528179485035586</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>1.048836820116197</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.54722706951156</v>
+        <v>-12.37531263024448</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.854977967879564</v>
+        <v>-1.786212192172735</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.528179485035586</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>1.047361593217456</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.64613380997083</v>
+        <v>-12.47421937070376</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.879487253898402</v>
+        <v>-1.810721478191572</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.627086225494861</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>1.003070959106763</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.44698170273374</v>
+        <v>-12.27506726346666</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.812877544650246</v>
+        <v>-1.744111768943415</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.461763699545048</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.089213341029968</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.22113655001433</v>
+        <v>-12.04922211074725</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.712960410526273</v>
+        <v>-1.644194634819443</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.419837023957884</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.123948419418475</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.93486173769163</v>
+        <v>-11.76294729842455</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.597311341041136</v>
+        <v>-1.528545565334305</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.419837023957884</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.125087563974533</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.98775702573592</v>
+        <v>-11.81584258646884</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.615835682096743</v>
+        <v>-1.547069906389912</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.414881677869438</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.130694545789709</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.70384829480717</v>
+        <v>-11.53193385554009</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.496538485486607</v>
+        <v>-1.427772709779776</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.414881677869438</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.136428250028346</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.58842737066907</v>
+        <v>-11.41651293140199</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.460107378225233</v>
+        <v>-1.391341602518403</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.299460753731342</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.195943542117338</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.324590503465</v>
+        <v>-11.15267606419792</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.364456112656514</v>
+        <v>-1.295690336949682</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.299460753731342</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.18606006080443</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.0573487025966</v>
+        <v>-10.88543426332953</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.259393952808528</v>
+        <v>-1.190628177101697</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.299460753731342</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.184225500305056</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.93404277411839</v>
+        <v>-10.76212833485131</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.210371896390701</v>
+        <v>-1.14160612068387</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.210043082603779</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.237575788008133</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.91008923314243</v>
+        <v>-10.73817479387535</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.200121973854824</v>
+        <v>-1.131356198147994</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.186089541627822</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.252616418739201</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.64602929481963</v>
+        <v>-10.47411485555255</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.107758314687458</v>
+        <v>-1.038992538980627</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-2.922029603305025</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.397792065571127</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.938949671314793</v>
+        <v>-9.767035232047716</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8277134989458235</v>
+        <v>-0.7589477232389927</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-2.922029603305025</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.395005031910826</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.898765372948603</v>
+        <v>-9.726850933681526</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.8112961557115059</v>
+        <v>-0.7425303800046752</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-2.881845304938834</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.419459234818382</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.818695577410798</v>
+        <v>-9.646781138143721</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7799014162756275</v>
+        <v>-0.7111356405687967</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.80177550940103</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.466867933361821</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.585214355181201</v>
+        <v>-9.413299915914124</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6785844985459359</v>
+        <v>-0.6098187228391052</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.568294287171432</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.614881095537433</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.405505825037327</v>
+        <v>-9.23359138577025</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.6095932968013456</v>
+        <v>-0.5408275210945148</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.511122783008736</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.646291787722091</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.27323035140644</v>
+        <v>-9.101315912139363</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5613156206019636</v>
+        <v>-0.4925498448951329</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.378847309377849</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.72102455864765</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.082630676733286</v>
+        <v>-8.910716237466209</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4822606900450657</v>
+        <v>-0.4134949143382349</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.188247634704697</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.838199424139178</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.833630878049705</v>
+        <v>-8.661716438782628</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3697544293479744</v>
+        <v>-0.3009886536411437</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.188247634704697</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.851105765362837</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.93922086782281</v>
+        <v>-8.767306428555733</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5399663548564351</v>
+        <v>-0.4712005791496043</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.293837624477801</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.659775841899756</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.957955769941407</v>
+        <v>-8.78604133067433</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4989159738267874</v>
+        <v>-0.4301501981199567</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.293837624477801</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.708320183776842</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.810015728533807</v>
+        <v>-8.63810128926673</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5596188799519153</v>
+        <v>-0.4908531042450845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.273516708569244</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.600633810633809</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.785787092144835</v>
+        <v>-8.613872652877758</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5586414116498046</v>
+        <v>-0.4898756359429735</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.249288072180271</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.606457006213714</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.742238685374144</v>
+        <v>-8.570324246107067</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5481826610366212</v>
+        <v>-0.4794168853297904</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.249288072180271</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.599496394118621</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.500090291920285</v>
+        <v>-8.328175852653208</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4368609492739348</v>
+        <v>-0.3680951735671041</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.249288072180271</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.613958748499764</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.436860920151938</v>
+        <v>-8.264946480884861</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4170370801074008</v>
+        <v>-0.3482713044005701</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.249288072180271</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.608490868958959</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.313569785334808</v>
+        <v>-8.141655346067731</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3702225321699717</v>
+        <v>-0.301456756463141</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.125996937363141</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.679963643859814</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.292420586431366</v>
+        <v>-8.120506147164289</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3540618743712698</v>
+        <v>-0.2852960986644391</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.104847738459698</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.700354141439206</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.04865514444792</v>
+        <v>-7.876740705180844</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2607749892308409</v>
+        <v>-0.1920092135240106</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.104847738459698</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.696134849786256</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.78462707725466</v>
+        <v>-7.612712637987585</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1530394484335207</v>
+        <v>-0.08427367272669084</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.902982339643744</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.716229739435599</v>
+        <v>1.819378402995844</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.534776683305585</v>
+        <v>-7.36286224403851</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.06035721587018861</v>
+        <v>0.008408559836641238</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.902982339643744</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.708971814419301</v>
+        <v>1.812120477979547</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.231209194301607</v>
+        <v>-7.059294755034531</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.06466890325205155</v>
+        <v>0.1334346789588814</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.902982339643744</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.71257093793995</v>
+        <v>1.815719601500195</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.157729285449593</v>
+        <v>-6.985814846182517</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1073883728474105</v>
+        <v>0.1761541485542408</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.001416870058805</v>
+        <v>-1.82950243079173</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.769986389305712</v>
+        <v>1.873135052865958</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.93269628578077</v>
+        <v>-6.760781846513694</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1964220503312371</v>
+        <v>0.2651878260380669</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.776383870389982</v>
+        <v>-1.604469431122907</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.904026666723303</v>
+        <v>2.007175330283548</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.718061908144363</v>
+        <v>-6.546147468877288</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2869706024401171</v>
+        <v>0.3557363781469469</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.3898350534865</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.037502094359464</v>
+        <v>2.14065075791971</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.451461551170011</v>
+        <v>-6.279547111902936</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3748050040136532</v>
+        <v>0.4435707797204835</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.3898350534865</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.01869635314326</v>
+        <v>2.121845016703505</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.211031054365151</v>
+        <v>-6.039116615098076</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4727202793604746</v>
+        <v>0.5414860550673049</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.14940455668164</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.164697727851054</v>
+        <v>2.267846391411299</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.968240246715705</v>
+        <v>-5.79632580744863</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.573765916255073</v>
+        <v>0.6425316919619033</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.14940455668164</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.168627041685874</v>
+        <v>2.271775705246119</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.85230039709052</v>
+        <v>-5.680385957823445</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6208204400224875</v>
+        <v>0.6895862157293173</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.072582825665516</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.215398664212888</v>
+        <v>2.318547327773133</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.609644808667356</v>
+        <v>-5.437730369400281</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7148807466117462</v>
+        <v>0.7836465223185765</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.072582825665516</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.212396735432882</v>
+        <v>2.315545398993127</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.389624010630346</v>
+        <v>-5.217709571363271</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8044681028371645</v>
+        <v>0.8732338785439948</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.103277419864611</v>
+        <v>-0.9313629805975359</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.298707679484284</v>
+        <v>2.401856343044529</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.190375380725537</v>
+        <v>-5.018460941458462</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9000617376009115</v>
+        <v>0.9688275133077418</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.103277419864611</v>
+        <v>-0.9313629805975359</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.314601862286107</v>
+        <v>2.417750525846352</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.030860277206167</v>
+        <v>-4.858945837939092</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9650136234489612</v>
+        <v>1.033779399155792</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9437623163452412</v>
+        <v>-0.7718478770781659</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.411456768838031</v>
+        <v>2.514605432398276</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.88618813210643</v>
+        <v>-4.714273692839354</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.032970584050296</v>
+        <v>1.101736359757126</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7990901712455039</v>
+        <v>-0.6271757319784286</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.508348158459313</v>
+        <v>2.611496822019558</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.946062959464122</v>
+        <v>-4.774148520197047</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.995058144508645</v>
+        <v>1.063823920215475</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.6870505593361207</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.458460753446124</v>
+        <v>2.561609417006369</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.859263461685114</v>
+        <v>-4.687349022418038</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.052178436942814</v>
+        <v>1.120944212649645</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.6870505593361207</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.48086124676869</v>
+        <v>2.584009910328935</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.86173316814692</v>
+        <v>-4.689818728879844</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.051262955731504</v>
+        <v>1.120028731438334</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.8614347050650022</v>
+        <v>-0.6895202657979269</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.479451824265018</v>
+        <v>2.582600487825264</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.93010335447093</v>
+        <v>-4.758188915203855</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.034921803676602</v>
+        <v>1.103687579383432</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.8521590060287872</v>
+        <v>-0.680244566761712</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.496024166161449</v>
+        <v>2.599172829721694</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.808686924844453</v>
+        <v>-4.636772485577378</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.073925084159084</v>
+        <v>1.142690859865914</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.8521590060287872</v>
+        <v>-0.680244566761712</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.486460874793341</v>
+        <v>2.589609538353586</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.839680084173159</v>
+        <v>-4.667765644906083</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8862373854679888</v>
+        <v>0.9550031611748189</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.8521590060287872</v>
+        <v>-0.680244566761712</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.311170439833727</v>
+        <v>2.414319103393972</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.664205824380689</v>
+        <v>-4.492291385113614</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9609943213767644</v>
+        <v>1.029760097083595</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.8521590060287872</v>
+        <v>-0.680244566761712</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.315737671825515</v>
+        <v>2.418886335385761</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.775142077021938</v>
+        <v>-4.603227637754863</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9166312942070625</v>
+        <v>0.9853970699138925</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.8521590060287872</v>
+        <v>-0.680244566761712</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.315749145712313</v>
+        <v>2.418897809272558</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.978168654565171</v>
+        <v>-4.806254215298096</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8385520484096747</v>
+        <v>0.9073178241165047</v>
       </c>
       <c r="F1941" t="n">
-        <v>-1.055185583572021</v>
+        <v>-0.8832711443049454</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.197064584406278</v>
+        <v>2.300213247966523</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.820243055629878</v>
+        <v>-4.648328616362803</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9118946744159242</v>
+        <v>0.9806604501227543</v>
       </c>
       <c r="F1942" t="n">
-        <v>-1.055185583572021</v>
+        <v>-0.8832711443049454</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.207236970838411</v>
+        <v>2.310385634398656</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.968564309441007</v>
+        <v>-4.796649870173932</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8475124434653329</v>
+        <v>0.9162782191721632</v>
       </c>
       <c r="F1943" t="n">
-        <v>-1.055185583572021</v>
+        <v>-0.8832711443049454</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.202183241412271</v>
+        <v>2.305331904972516</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.969747394092067</v>
+        <v>-4.797832954824992</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8388149850494344</v>
+        <v>0.9075807607562645</v>
       </c>
       <c r="F1944" t="n">
-        <v>-1.060828632038532</v>
+        <v>-0.8889141927714569</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.19057318777689</v>
+        <v>2.293721851337135</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.846619687097984</v>
+        <v>-4.674705247830909</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8886179408801691</v>
+        <v>0.9573837165869992</v>
       </c>
       <c r="F1945" t="n">
-        <v>-1.060828632038532</v>
+        <v>-0.8889141927714569</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.191125060809991</v>
+        <v>2.294273724370236</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.753809205647125</v>
+        <v>-4.581894766380049</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8550148253518786</v>
+        <v>0.9237806010587089</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.9680181505876729</v>
+        <v>-0.7961037113205975</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.176084041571873</v>
+        <v>2.279232705132118</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.705246153426095</v>
+        <v>-4.533331714159019</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8763135221648914</v>
+        <v>0.9450792978717215</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.9194550983666427</v>
+        <v>-0.7475406590995674</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.207095348829091</v>
+        <v>2.310244012389337</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.592574935189845</v>
+        <v>-4.420660495922769</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9164577179711144</v>
+        <v>0.9852234936779447</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.8067838801303926</v>
+        <v>-0.6348694408633171</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.269773788282564</v>
+        <v>2.37292245184281</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.40791224852914</v>
+        <v>3.857569504314657</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.48541628038723</v>
+        <v>-4.298154790560517</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9648124757228276</v>
+        <v>1.039717071653513</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.8067838801303926</v>
+        <v>-0.6348694408633171</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.275265084113232</v>
+        <v>2.378413747673477</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-703.4%</t>
+          <t>-720.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-58.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>440.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-591.4%</t>
+          <t>-622.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-281.8%</t>
+          <t>-288.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-512.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-272.3%</t>
+          <t>-284.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-327.7%</t>
+          <t>-344.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-166.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-287.5%</t>
+          <t>-320.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-197.0%</t>
+          <t>-207.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-208.2%</t>
+          <t>-228.1%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.06255252149029</v>
+        <v>-1.234466960757366</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.691703017041166</v>
+        <v>2.622937241334336</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.072284030854885</v>
+        <v>0.9003695915878102</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.760450868463961</v>
+        <v>3.657302204903716</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.284174455048408</v>
+        <v>-1.456088894315483</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.602920460216841</v>
+        <v>2.53415468451001</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.034757897167516</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.737801404850461</v>
+        <v>3.634652741290216</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.492178513401485</v>
+        <v>-1.66409295266856</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.524610981429535</v>
+        <v>2.455845205722705</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.034757897167516</v>
+        <v>0.8628434579004411</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.742693549404386</v>
+        <v>3.639544885844141</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.70359093428946</v>
+        <v>-1.875505373556535</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.435127469412333</v>
+        <v>2.366361693705503</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8233454762795409</v>
+        <v>0.6514310370124661</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.610927553209589</v>
+        <v>3.507778889649344</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.042749311877983</v>
+        <v>-2.214663751145058</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.292548417683373</v>
+        <v>2.223782641976543</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4841870986910188</v>
+        <v>0.312272659423944</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.400516825962925</v>
+        <v>3.29736816240268</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.370766533605462</v>
+        <v>-2.542680972872537</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.18167981873115</v>
+        <v>2.11291404302432</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1561698769635397</v>
+        <v>-0.01574456230353516</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.224044782665206</v>
+        <v>3.120896119104961</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.86409140514064</v>
+        <v>-3.036005844407715</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.992448620525647</v>
+        <v>1.923682844818817</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.05118376272392094</v>
+        <v>-0.1207306765431539</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.169151864530003</v>
+        <v>3.066003200969758</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.356476433164737</v>
+        <v>-3.528390872431812</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.796601001359741</v>
+        <v>1.727835225652911</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4412012653001758</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.874827239759278</v>
+        <v>2.771678576199033</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.741656824094809</v>
+        <v>-3.913571263361884</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.641071383800575</v>
+        <v>1.572305608093745</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4412012653001758</v>
+        <v>-0.6131157045672506</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.873369778572141</v>
+        <v>2.770221115011896</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.085339597321472</v>
+        <v>-4.257254036588547</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.505367397964526</v>
+        <v>1.436601622257696</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5491073173273939</v>
+        <v>-0.7210217565944688</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.810395270810426</v>
+        <v>2.707246607250181</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.44298994755982</v>
+        <v>-4.614904386826895</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.358413316525445</v>
+        <v>1.289647540818615</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9067576675657421</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.591911119323675</v>
+        <v>2.48876245576343</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.752224050555871</v>
+        <v>-4.924138489822946</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.236492602027284</v>
+        <v>1.167726826320454</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9067576675657421</v>
+        <v>-1.078672106832817</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.593684046023935</v>
+        <v>2.49053538246369</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.184029843705658</v>
+        <v>-5.355944282972733</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.050103172234774</v>
+        <v>0.9813373965279433</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.043175164007009</v>
+        <v>-1.215089603274084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.498166435626579</v>
+        <v>2.395017772066334</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.41872383783821</v>
+        <v>-5.590638277105286</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9445103495838429</v>
+        <v>0.8757445738770131</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.036838896777754</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.490252970966222</v>
+        <v>2.387104307405978</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.754386485068663</v>
+        <v>-5.926300924335738</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8088258823476271</v>
+        <v>0.7400601066407972</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.036838896777754</v>
+        <v>-1.208753336044829</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.488833562622188</v>
+        <v>2.385684899061943</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.118012729968976</v>
+        <v>-6.289927169236051</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6698629446217432</v>
+        <v>0.6010971689149134</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.13506053364488</v>
+        <v>-1.306974972911954</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.436388140736154</v>
+        <v>2.333239477175909</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.483140112607723</v>
+        <v>-6.655054551874798</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5230665065720763</v>
+        <v>0.454300730865246</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.431371317943892</v>
+        <v>-1.603285757210967</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.257856185162578</v>
+        <v>2.154707521602333</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.891728889788402</v>
+        <v>-7.063643329055477</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3583925397145635</v>
+        <v>0.2896267640077337</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.01146446286893</v>
+        <v>1.908315799308685</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.304711373929496</v>
+        <v>-7.476625813196571</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1883849785295868</v>
+        <v>0.1196192028227565</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.006649895340391</v>
+        <v>1.903501231780145</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.721103248216493</v>
+        <v>-7.893017687483568</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.0198222794236651</v>
+        <v>-0.04894349628316519</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.004643945949268</v>
+        <v>1.901495282389023</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.097780258746337</v>
+        <v>-8.269694698013412</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1205898341195932</v>
+        <v>-0.1893556098264235</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.014902636617947</v>
+        <v>1.911753973057702</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.443655080731146</v>
+        <v>-8.615569519998221</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2628401977678219</v>
+        <v>-0.3316059734746521</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.011002201763642</v>
+        <v>1.907853538203397</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.605797351194239</v>
+        <v>-8.777711790461314</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.329292185898058</v>
+        <v>-0.3980579616048883</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.83996009512457</v>
+        <v>-2.011874534391645</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.009407121818643</v>
+        <v>1.906258458258398</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.902458693004437</v>
+        <v>-9.074373132271512</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4441777466929291</v>
+        <v>-0.5129435223997594</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.908703230858449</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.971940216307524</v>
+        <v>1.868791552747279</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.335807801114672</v>
+        <v>-9.507722240381748</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6215436944714265</v>
+        <v>-0.6903094701782564</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.908703230858449</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.967913911773121</v>
+        <v>1.864765248212876</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.718809189857303</v>
+        <v>-9.890723629124379</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.774846351290063</v>
+        <v>-0.8436121269968933</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.908703230858449</v>
+        <v>-2.080617670125524</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.967811810451537</v>
+        <v>1.864663146891292</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.876208070070424</v>
+        <v>-10.0481225093375</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8352343874038812</v>
+        <v>-0.9040001631107111</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.06610211107157</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.875943998295094</v>
+        <v>1.772795334734849</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.23573839257443</v>
+        <v>-10.4076528318415</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9736962131074316</v>
+        <v>-1.042461988814262</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.06610211107157</v>
+        <v>-2.238016550338645</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.881294301593144</v>
+        <v>1.778145638032899</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.56213842123944</v>
+        <v>-10.73405286050651</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.096340204616259</v>
+        <v>-1.165105980323089</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.392502139736583</v>
+        <v>-2.564416579003658</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.693370304351314</v>
+        <v>1.590221640791069</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.78128738931364</v>
+        <v>-10.95320182858071</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.18095804122417</v>
+        <v>-1.249723816930999</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.61165110781078</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.564922674128564</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.77759646435723</v>
+        <v>-10.9495109036243</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.179481671241605</v>
+        <v>-1.248247446948435</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.61165110781078</v>
+        <v>-2.783565547077855</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.564922674128564</v>
+        <v>1.461774010568319</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.98185463968709</v>
+        <v>-11.15376907895416</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.255671744254908</v>
+        <v>-1.324437519961738</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.739290052424769</v>
+        <v>-2.911204491691844</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.493852504478814</v>
+        <v>1.390703840918569</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.19989241131827</v>
+        <v>-11.37180685058534</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.338404298422943</v>
+        <v>-1.407170074129774</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.914060820520668</v>
+        <v>-3.085975259787743</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.39347259810571</v>
+        <v>1.290323934545465</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.12642257965082</v>
+        <v>-11.29833701891789</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.293644664262542</v>
+        <v>-1.362410439969373</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.84059098885322</v>
+        <v>-3.012505428120295</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.4529261985996</v>
+        <v>1.349777535039355</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.30154699703736</v>
+        <v>-11.47346143630444</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.349139210469643</v>
+        <v>-1.417904986176473</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.015715406239764</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.362406768915191</v>
+        <v>1.259258105354946</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.53599909105185</v>
+        <v>-11.70791353031893</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.450139212977035</v>
+        <v>-1.518904988683865</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.015715406239764</v>
+        <v>-3.187629845506839</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.355187604013595</v>
+        <v>1.25203894045335</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.82380293558909</v>
+        <v>-11.99571737485616</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.571932941565907</v>
+        <v>-1.640698717272736</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.303519250777002</v>
+        <v>-3.475433690044077</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.175833106517276</v>
+        <v>1.072684442957031</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.05362738275291</v>
+        <v>-12.22554182201999</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.66274693059288</v>
+        <v>-1.731512706299711</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.466166787847162</v>
+        <v>-3.638081227114237</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.079360374113736</v>
+        <v>0.9762117105534909</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.28565630248918</v>
+        <v>-12.45757074175625</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.752864769858271</v>
+        <v>-1.821630545565101</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.528179485035586</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.044846484429796</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.23364078852036</v>
+        <v>-12.40555522778744</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.728068228584345</v>
+        <v>-1.796834004291174</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.528179485035586</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.048836820116197</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.37531263024448</v>
+        <v>-12.54722706951156</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.786212192172735</v>
+        <v>-1.854977967879564</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.528179485035586</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.047361593217456</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.47421937070376</v>
+        <v>-12.64613380997083</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.810721478191572</v>
+        <v>-1.879487253898402</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.627086225494861</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.003070959106763</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.27506726346666</v>
+        <v>-12.44698170273374</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.744111768943415</v>
+        <v>-1.812877544650246</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.461763699545048</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.089213341029968</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.04922211074725</v>
+        <v>-12.22113655001433</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.644194634819443</v>
+        <v>-1.712960410526273</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.419837023957884</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.123948419418475</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.76294729842455</v>
+        <v>-11.93486173769163</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.528545565334305</v>
+        <v>-1.597311341041136</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.419837023957884</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.125087563974533</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.81584258646884</v>
+        <v>-11.98775702573592</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.547069906389912</v>
+        <v>-1.615835682096743</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.414881677869438</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.130694545789709</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.53193385554009</v>
+        <v>-11.70384829480717</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.427772709779776</v>
+        <v>-1.496538485486607</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.414881677869438</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.136428250028346</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.41651293140199</v>
+        <v>-11.58842737066907</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.391341602518403</v>
+        <v>-1.460107378225233</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.299460753731342</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.195943542117338</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.15267606419792</v>
+        <v>-11.324590503465</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.295690336949682</v>
+        <v>-1.364456112656514</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.299460753731342</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.18606006080443</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.88543426332953</v>
+        <v>-11.0573487025966</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.190628177101697</v>
+        <v>-1.259393952808528</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.299460753731342</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.184225500305056</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.76212833485131</v>
+        <v>-10.93404277411839</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.14160612068387</v>
+        <v>-1.210371896390701</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.210043082603779</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.237575788008133</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.73817479387535</v>
+        <v>-10.91008923314243</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.131356198147994</v>
+        <v>-1.200121973854824</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.186089541627822</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.252616418739201</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.47411485555255</v>
+        <v>-10.64602929481963</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.038992538980627</v>
+        <v>-1.107758314687458</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.922029603305025</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.397792065571127</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.767035232047716</v>
+        <v>-9.938949671314793</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7589477232389927</v>
+        <v>-0.8277134989458235</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.922029603305025</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.395005031910826</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.726850933681526</v>
+        <v>-9.898765372948603</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7425303800046752</v>
+        <v>-0.8112961557115059</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.881845304938834</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.419459234818382</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.646781138143721</v>
+        <v>-9.818695577410798</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7111356405687967</v>
+        <v>-0.7799014162756275</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.80177550940103</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.466867933361821</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.413299915914124</v>
+        <v>-9.585214355181201</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6098187228391052</v>
+        <v>-0.6785844985459359</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.568294287171432</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.614881095537433</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.23359138577025</v>
+        <v>-9.405505825037327</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5408275210945148</v>
+        <v>-0.6095932968013456</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.511122783008736</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.646291787722091</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.101315912139363</v>
+        <v>-9.27323035140644</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4925498448951329</v>
+        <v>-0.5613156206019636</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.378847309377849</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.72102455864765</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.910716237466209</v>
+        <v>-9.082630676733286</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4134949143382349</v>
+        <v>-0.4822606900450657</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.188247634704697</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.838199424139178</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.661716438782628</v>
+        <v>-8.833630878049705</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3009886536411437</v>
+        <v>-0.3697544293479744</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.188247634704697</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.851105765362837</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.767306428555733</v>
+        <v>-8.93922086782281</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4712005791496043</v>
+        <v>-0.5399663548564351</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.293837624477801</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.659775841899756</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.78604133067433</v>
+        <v>-8.957955769941407</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4301501981199567</v>
+        <v>-0.4989159738267874</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.293837624477801</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.708320183776842</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.63810128926673</v>
+        <v>-8.810015728533807</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4908531042450845</v>
+        <v>-0.5596188799519153</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.273516708569244</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.600633810633809</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.613872652877758</v>
+        <v>-8.785787092144835</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4898756359429735</v>
+        <v>-0.5586414116498046</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.249288072180271</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.606457006213714</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.570324246107067</v>
+        <v>-8.742238685374144</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4794168853297904</v>
+        <v>-0.5481826610366212</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.249288072180271</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.599496394118621</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.328175852653208</v>
+        <v>-8.500090291920285</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3680951735671041</v>
+        <v>-0.4368609492739348</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.249288072180271</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.613958748499764</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.264946480884861</v>
+        <v>-8.436860920151938</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3482713044005701</v>
+        <v>-0.4170370801074008</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.249288072180271</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.608490868958959</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.141655346067731</v>
+        <v>-8.313569785334808</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.301456756463141</v>
+        <v>-0.3702225321699717</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.125996937363141</v>
+        <v>-2.297911376630216</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.679963643859814</v>
+        <v>1.576814980299569</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.120506147164289</v>
+        <v>-8.292420586431366</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2852960986644391</v>
+        <v>-0.3540618743712698</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.104847738459698</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.700354141439206</v>
+        <v>1.59720547787896</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.876740705180844</v>
+        <v>-8.04865514444792</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1920092135240106</v>
+        <v>-0.2607749892308409</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.104847738459698</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.696134849786256</v>
+        <v>1.592986186226011</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.612712637987585</v>
+        <v>-7.916128346848719</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08427367272669084</v>
+        <v>-0.2056399562711446</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.902982339643744</v>
+        <v>-2.235710363513278</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.819378402995844</v>
+        <v>1.619741588674124</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.36286224403851</v>
+        <v>-7.666277952899645</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.008408559836641238</v>
+        <v>-0.1129577237078125</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.902982339643744</v>
+        <v>-2.235710363513278</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.812120477979547</v>
+        <v>1.612483663657826</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.059294755034531</v>
+        <v>-7.362710463895666</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1334346789588814</v>
+        <v>0.01206839541442761</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.902982339643744</v>
+        <v>-2.235710363513278</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.815719601500195</v>
+        <v>1.616082787178475</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.985814846182517</v>
+        <v>-7.289230555043652</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1761541485542408</v>
+        <v>0.05478786500978705</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.82950243079173</v>
+        <v>-2.162230454661263</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.873135052865958</v>
+        <v>1.673498238544237</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.760781846513694</v>
+        <v>-7.064197555374829</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2651878260380669</v>
+        <v>0.1438215424936131</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.604469431122907</v>
+        <v>-1.93719745499244</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.007175330283548</v>
+        <v>1.807538515961828</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.546147468877288</v>
+        <v>-6.849563177738422</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3557363781469469</v>
+        <v>0.2343700946024931</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.3898350534865</v>
+        <v>-1.722563077356034</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.14065075791971</v>
+        <v>1.94101394359799</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.279547111902936</v>
+        <v>-6.58296282076407</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4435707797204835</v>
+        <v>0.3222044961760298</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.3898350534865</v>
+        <v>-1.722563077356034</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.121845016703505</v>
+        <v>1.922208202381785</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.039116615098076</v>
+        <v>-6.34253232395921</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5414860550673049</v>
+        <v>0.4201197715228511</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.14940455668164</v>
+        <v>-1.482132580551173</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.267846391411299</v>
+        <v>2.068209577089579</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.79632580744863</v>
+        <v>-6.099741516309765</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6425316919619033</v>
+        <v>0.5211654084174495</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.14940455668164</v>
+        <v>-1.482132580551173</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.271775705246119</v>
+        <v>2.072138890924399</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.680385957823445</v>
+        <v>-5.983801666684579</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6895862157293173</v>
+        <v>0.5682199321848636</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.072582825665516</v>
+        <v>-1.405310849535049</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.318547327773133</v>
+        <v>2.118910513451413</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.437730369400281</v>
+        <v>-5.741146078261416</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7836465223185765</v>
+        <v>0.6622802387741227</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.072582825665516</v>
+        <v>-1.405310849535049</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.315545398993127</v>
+        <v>2.115908584671407</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.217709571363271</v>
+        <v>-5.521125280224405</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8732338785439948</v>
+        <v>0.751867594999541</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9313629805975359</v>
+        <v>-1.264091004467069</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.401856343044529</v>
+        <v>2.202219528722809</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.018460941458462</v>
+        <v>-5.321876650319596</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9688275133077418</v>
+        <v>0.847461229763288</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9313629805975359</v>
+        <v>-1.264091004467069</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.417750525846352</v>
+        <v>2.218113711524632</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.858945837939092</v>
+        <v>-5.162361546800226</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.033779399155792</v>
+        <v>0.9124131156113378</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7718478770781659</v>
+        <v>-1.104575900947699</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.514605432398276</v>
+        <v>2.314968618076556</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.714273692839354</v>
+        <v>-5.017689401700489</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.101736359757126</v>
+        <v>0.9803700762126724</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6271757319784286</v>
+        <v>-0.9599037558479617</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.611496822019558</v>
+        <v>2.411860007697839</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.774148520197047</v>
+        <v>-5.077564229058181</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.063823920215475</v>
+        <v>0.9424576366710213</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6870505593361207</v>
+        <v>-1.019778583205654</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.561609417006369</v>
+        <v>2.361972602684649</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.687349022418038</v>
+        <v>-4.990764731279173</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.120944212649645</v>
+        <v>0.9995779291051909</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6870505593361207</v>
+        <v>-1.019778583205654</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.584009910328935</v>
+        <v>2.384373096007215</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.689818728879844</v>
+        <v>-4.993234437740979</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.120028731438334</v>
+        <v>0.9986624478938806</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6895202657979269</v>
+        <v>-1.02224828966746</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.582600487825264</v>
+        <v>2.382963673503544</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.758188915203855</v>
+        <v>-5.061604624064989</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.103687579383432</v>
+        <v>0.9823212958389784</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.680244566761712</v>
+        <v>-1.012972590631245</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.599172829721694</v>
+        <v>2.399536015399975</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.636772485577378</v>
+        <v>-4.940188194438512</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.142690859865914</v>
+        <v>1.02132457632146</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.680244566761712</v>
+        <v>-1.012972590631245</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.589609538353586</v>
+        <v>2.389972724031866</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.667765644906083</v>
+        <v>-4.971181353767218</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9550031611748189</v>
+        <v>0.8336368776303651</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.680244566761712</v>
+        <v>-1.012972590631245</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.414319103393972</v>
+        <v>2.214682289072253</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.492291385113614</v>
+        <v>-4.795707093974748</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.029760097083595</v>
+        <v>0.9083938135391407</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.680244566761712</v>
+        <v>-1.012972590631245</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.418886335385761</v>
+        <v>2.21924952106404</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.603227637754863</v>
+        <v>-4.906643346615997</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9853970699138925</v>
+        <v>0.8640307863694388</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.680244566761712</v>
+        <v>-1.012972590631245</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.418897809272558</v>
+        <v>2.219260994950838</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.806254215298096</v>
+        <v>-5.10966992415923</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9073178241165047</v>
+        <v>0.785951540572051</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8832711443049454</v>
+        <v>-1.215999168174479</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.300213247966523</v>
+        <v>2.100576433644803</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.648328616362803</v>
+        <v>-4.951744325223937</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9806604501227543</v>
+        <v>0.8592941665783005</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8832711443049454</v>
+        <v>-1.215999168174479</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.310385634398656</v>
+        <v>2.110748820076936</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.796649870173932</v>
+        <v>-5.100065579035066</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9162782191721632</v>
+        <v>0.7949119356277095</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8832711443049454</v>
+        <v>-1.215999168174479</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.305331904972516</v>
+        <v>2.105695090650796</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.797832954824992</v>
+        <v>-5.101248663686127</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9075807607562645</v>
+        <v>0.7862144772118107</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8889141927714569</v>
+        <v>-1.22164221664099</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.293721851337135</v>
+        <v>2.094085037015415</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.674705247830909</v>
+        <v>-4.978120956692043</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9573837165869992</v>
+        <v>0.8360174330425454</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8889141927714569</v>
+        <v>-1.22164221664099</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.294273724370236</v>
+        <v>2.094636910048516</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.581894766380049</v>
+        <v>-4.885310475241184</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9237806010587089</v>
+        <v>0.8024143175142551</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7961037113205975</v>
+        <v>-1.128831735190131</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.279232705132118</v>
+        <v>2.079595890810397</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.533331714159019</v>
+        <v>-4.836747423020154</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9450792978717215</v>
+        <v>0.8237130143272677</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7475406590995674</v>
+        <v>-1.080268682969101</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.310244012389337</v>
+        <v>2.110607198067616</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.420660495922769</v>
+        <v>-4.724076204783904</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9852234936779447</v>
+        <v>0.8638572101334909</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6348694408633171</v>
+        <v>-0.9675974647328505</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.37292245184281</v>
+        <v>2.17328563752109</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.857569504314657</v>
+        <v>3.384652976805205</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.298154790560517</v>
+        <v>-4.611699203601231</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.039717071653513</v>
+        <v>0.9142993064372273</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6348694408633171</v>
+        <v>-0.9675974647328505</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.378413747673477</v>
+        <v>2.178776933351757</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -605,21 +605,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-48.0%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>137.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.3%</t>
+          <t>440.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-512.1%</t>
+          <t>-512.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-228.1%</t>
+          <t>-183.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1949"/>
+  <dimension ref="A1:G1950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.384652976805205</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
@@ -46388,6 +46388,29 @@
       </c>
       <c r="G1949" t="n">
         <v>2.178776933351757</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B1950" t="n">
+        <v>3.392357698660958</v>
+      </c>
+      <c r="C1950" t="n">
+        <v>2.636696816378729</v>
+      </c>
+      <c r="D1950" t="n">
+        <v>-4.611699203601231</v>
+      </c>
+      <c r="E1950" t="n">
+        <v>0.9142993064372273</v>
+      </c>
+      <c r="F1950" t="n">
+        <v>-0.9675974647328505</v>
+      </c>
+      <c r="G1950" t="n">
+        <v>2.629760613365097</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-28.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.1%</t>
+          <t>137.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-720.6%</t>
+          <t>-722.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.4%</t>
+          <t>443.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-622.7%</t>
+          <t>-611.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-288.6%</t>
+          <t>-289.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-512.2%</t>
+          <t>-124.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.8%</t>
+          <t>-280.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-338.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-164.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-320.8%</t>
+          <t>-298.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-203.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.0%</t>
+          <t>-163.4%</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.456088894315483</v>
+        <v>-1.472676064258206</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.53415468451001</v>
+        <v>2.527519816532922</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.9284112382299099</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.673993409487897</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.66409295266856</v>
+        <v>-1.680680122611283</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.455845205722705</v>
+        <v>2.449210337745616</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.9284112382299099</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.678885554041822</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.875505373556535</v>
+        <v>-1.892092543499258</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.366361693705503</v>
+        <v>2.359726825728414</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.7169988173419348</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.547119557847026</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.214663751145058</v>
+        <v>-2.23125092108778</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.223782641976543</v>
+        <v>2.217147773999454</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.3778404397534127</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.336708830600362</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.542680972872537</v>
+        <v>-2.559268142815259</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.11291404302432</v>
+        <v>2.106279175047231</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>0.04982321802593359</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.160236787302642</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.036005844407715</v>
+        <v>-3.052593014350438</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.923682844818817</v>
+        <v>1.917047976841728</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.05516289621368514</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.10534386916744</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.528390872431812</v>
+        <v>-3.544978042374535</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.727835225652911</v>
+        <v>1.721200357675821</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5475479242377819</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.811019244396714</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.913571263361884</v>
+        <v>-3.930158433304607</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.572305608093745</v>
+        <v>1.565670740116656</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.5475479242377819</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.809561783209577</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.257254036588547</v>
+        <v>-4.273841206531269</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.436601622257696</v>
+        <v>1.429966754280607</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.655453976265</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.746587275447862</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.614904386826895</v>
+        <v>-4.631491556769618</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.289647540818615</v>
+        <v>1.283012672841526</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.013104326503348</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.528103123961111</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.924138489822946</v>
+        <v>-4.940725659765668</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.167726826320454</v>
+        <v>1.161091958343365</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.013104326503348</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.529876050661371</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.355944282972733</v>
+        <v>-5.372531452915456</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9813373965279433</v>
+        <v>0.9747025285508544</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.149521822944615</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.434358440264015</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.590638277105286</v>
+        <v>-5.607225447048008</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8757445738770131</v>
+        <v>0.8691097058999242</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.14318555571536</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.426444975603659</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.926300924335738</v>
+        <v>-5.942888094278461</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7400601066407972</v>
+        <v>0.7334252386637083</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.14318555571536</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.425025567259624</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.289927169236051</v>
+        <v>-6.306514339178774</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6010971689149134</v>
+        <v>0.5944623009378245</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.241407192582486</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.37258014537359</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.655054551874798</v>
+        <v>-6.671641721817521</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.454300730865246</v>
+        <v>0.4476658628881571</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.537717976881498</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.194048189800014</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.063643329055477</v>
+        <v>-7.080230498998199</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2896267640077337</v>
+        <v>0.2829918960306443</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.947656467506366</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.476625813196571</v>
+        <v>-7.493212983139293</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1196192028227565</v>
+        <v>0.1129843348456676</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.942841899977827</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.893017687483568</v>
+        <v>-7.909604857426291</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.04894349628316519</v>
+        <v>-0.05557836426025409</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.940835950586704</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.269694698013412</v>
+        <v>-8.286281867956134</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1893556098264235</v>
+        <v>-0.1959904778035124</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.951094641255383</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.615569519998221</v>
+        <v>-8.632156689940944</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3316059734746521</v>
+        <v>-0.338240841451741</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.947194206401078</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.777711790461314</v>
+        <v>-8.794298960404037</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3980579616048883</v>
+        <v>-0.4046928295819772</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.946306754062177</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.945599126456079</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.074373132271512</v>
+        <v>-9.090960302214235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5129435223997594</v>
+        <v>-0.5195783903768483</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.015049889796055</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.90813222094496</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.507722240381748</v>
+        <v>-9.52430941032447</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6903094701782564</v>
+        <v>-0.6969443381553457</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.015049889796055</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.904105916410557</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.890723629124379</v>
+        <v>-9.907310799067101</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8436121269968933</v>
+        <v>-0.8502469949739822</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.015049889796055</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.904003815088973</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.0481225093375</v>
+        <v>-10.06470967928022</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9040001631107111</v>
+        <v>-0.9106350310878004</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.172448770009177</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.81213600293253</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4076528318415</v>
+        <v>-10.42424000178422</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.042461988814262</v>
+        <v>-1.04909685679135</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.172448770009177</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.81748630623058</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.73405286050651</v>
+        <v>-10.75064003044924</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.165105980323089</v>
+        <v>-1.171740848300179</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.49884879867419</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.62956230898875</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.95320182858071</v>
+        <v>-10.96978899852343</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.249723816930999</v>
+        <v>-1.256358684908089</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.717997766748387</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.501114678766001</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9495109036243</v>
+        <v>-10.96609807356702</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.248247446948435</v>
+        <v>-1.254882314925525</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.717997766748387</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.501114678766001</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.15376907895416</v>
+        <v>-11.17035624889689</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.324437519961738</v>
+        <v>-1.331072387938828</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.845636711362376</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.430044509116249</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.37180685058534</v>
+        <v>-11.38839402052806</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.407170074129774</v>
+        <v>-1.413804942106862</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.020407479458275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.329664602743146</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.29833701891789</v>
+        <v>-11.31492418886062</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.362410439969373</v>
+        <v>-1.369045307946462</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-2.946937647790826</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.389118203237036</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.47346143630444</v>
+        <v>-11.49004860624716</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.417904986176473</v>
+        <v>-1.424539854153562</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.12206206517737</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.298598773552627</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.70791353031893</v>
+        <v>-11.72450070026165</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.518904988683865</v>
+        <v>-1.525539856660954</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.12206206517737</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.291379608651031</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.99571737485616</v>
+        <v>-12.01230454479889</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.640698717272736</v>
+        <v>-1.647333585249826</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.409865909714608</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.112025111154712</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.22554182201999</v>
+        <v>-12.24212899196271</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.731512706299711</v>
+        <v>-1.738147574276799</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.572513446784769</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>1.015552378751172</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.45757074175625</v>
+        <v>-12.47415791169897</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.821630545565101</v>
+        <v>-1.828265413542189</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.634526143973192</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9810384890672328</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.40555522778744</v>
+        <v>-12.42214239773016</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.796834004291174</v>
+        <v>-1.803468872268263</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.634526143973192</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9850288247536336</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.54722706951156</v>
+        <v>-12.56381423945428</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.854977967879564</v>
+        <v>-1.861612835856653</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.634526143973192</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.9835535978548919</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.64613380997083</v>
+        <v>-12.66272097991356</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.879487253898402</v>
+        <v>-1.886122121875491</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.733432884432468</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.9392629637441985</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.44698170273374</v>
+        <v>-12.46356887267646</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.812877544650246</v>
+        <v>-1.819512412627335</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.568110358482655</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.025405345667404</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.22113655001433</v>
+        <v>-12.23772371995705</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.712960410526273</v>
+        <v>-1.719595278503361</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.526183682895491</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.06014042405591</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.93486173769163</v>
+        <v>-11.95144890763435</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.597311341041136</v>
+        <v>-1.603946209018224</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.526183682895491</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.061279568611969</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.98775702573592</v>
+        <v>-12.00434419567864</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.615835682096743</v>
+        <v>-1.622470550073831</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.521228336807045</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.066886550427145</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.70384829480717</v>
+        <v>-11.72043546474989</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.496538485486607</v>
+        <v>-1.503173353463695</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.521228336807045</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.072620254665781</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.58842737066907</v>
+        <v>-11.60501454061179</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.460107378225233</v>
+        <v>-1.466742246202322</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.405807412668949</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.132135546754773</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.324590503465</v>
+        <v>-11.34117767340772</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.364456112656514</v>
+        <v>-1.371090980633601</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.405807412668949</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.122252065441866</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.0573487025966</v>
+        <v>-11.07393587253932</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.259393952808528</v>
+        <v>-1.266028820785616</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.405807412668949</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.120417504942492</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.93404277411839</v>
+        <v>-10.95062994406111</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.210371896390701</v>
+        <v>-1.21700676436779</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.316389741541386</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.173767792645569</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.91008923314243</v>
+        <v>-10.92667640308515</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.200121973854824</v>
+        <v>-1.206756841831913</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.292436200565429</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.188808423376637</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.64602929481963</v>
+        <v>-10.66261646476235</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.107758314687458</v>
+        <v>-1.114393182664546</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.028376262242632</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.333984070208563</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.938949671314793</v>
+        <v>-9.955536841257514</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8277134989458235</v>
+        <v>-0.8343483669229119</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.028376262242632</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.331197036548262</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.898765372948603</v>
+        <v>-9.915352542891323</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.8112961557115059</v>
+        <v>-0.8179310236885944</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-2.988191963876441</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.355651239455818</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.818695577410798</v>
+        <v>-9.835282747353519</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7799014162756275</v>
+        <v>-0.7865362842527155</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.908122168338637</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.403059937999257</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.585214355181201</v>
+        <v>-9.601801525123921</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6785844985459359</v>
+        <v>-0.6852193665230244</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.674640946109039</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.551073100174869</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.405505825037327</v>
+        <v>-9.422092994980048</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.6095932968013456</v>
+        <v>-0.616228164778434</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.617469441946343</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.582483792359527</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.27323035140644</v>
+        <v>-9.289817521349161</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5613156206019636</v>
+        <v>-0.5679504885790521</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.485193968315456</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.657216563285086</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.082630676733286</v>
+        <v>-9.099217846676007</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4822606900450657</v>
+        <v>-0.4888955580221541</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.294594293642304</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.774391428776614</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.833630878049705</v>
+        <v>-8.850218047992426</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3697544293479744</v>
+        <v>-0.3763892973250629</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.294594293642304</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.787297770000273</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.93922086782281</v>
+        <v>-8.95580803776553</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5399663548564351</v>
+        <v>-0.5466012228335231</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.400184283415408</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.595967846537192</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.957955769941407</v>
+        <v>-8.974542939884127</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4989159738267874</v>
+        <v>-0.5055508418038759</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.400184283415408</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.644512188414278</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.810015728533807</v>
+        <v>-8.826602898476528</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5596188799519153</v>
+        <v>-0.5662537479290037</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.379863367506851</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.536825815271245</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.785787092144835</v>
+        <v>-8.802374262087556</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5586414116498046</v>
+        <v>-0.5652762796268926</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.355634731117878</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.54264901085115</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.742238685374144</v>
+        <v>-8.758825855316864</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5481826610366212</v>
+        <v>-0.5548175290137092</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.355634731117878</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.535688398756057</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.500090291920285</v>
+        <v>-8.516677461863006</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4368609492739348</v>
+        <v>-0.4434958172510228</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.355634731117878</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.5501507531372</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.436860920151938</v>
+        <v>-8.453448090094659</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4170370801074008</v>
+        <v>-0.4236719480844888</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.355634731117878</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.544682873596395</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.313569785334808</v>
+        <v>-8.330156955277529</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3702225321699717</v>
+        <v>-0.3768574001470602</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.232343596300748</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.61615564849725</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.292420586431366</v>
+        <v>-8.309007756374086</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3540618743712698</v>
+        <v>-0.3606967423483578</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.211194397397305</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.636546146076641</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.04865514444792</v>
+        <v>-8.065242314390641</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2607749892308409</v>
+        <v>-0.2674098572079293</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.211194397397305</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.632326854423692</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.916128346848719</v>
+        <v>-7.801214247197381</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.2056399562711446</v>
+        <v>-0.1596743164106091</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.235710363513278</v>
+        <v>-2.009328998581351</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.619741588674124</v>
+        <v>1.75557040763328</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.666277952899645</v>
+        <v>-7.551363853248306</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.1129577237078125</v>
+        <v>-0.06699208384727706</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.235710363513278</v>
+        <v>-2.009328998581351</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.612483663657826</v>
+        <v>1.748312482616982</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.362710463895666</v>
+        <v>-7.247796364244327</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.01206839541442761</v>
+        <v>0.05803403527496309</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.235710363513278</v>
+        <v>-2.009328998581351</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.616082787178475</v>
+        <v>1.751911606137631</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.289230555043652</v>
+        <v>-7.174316455392313</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.05478786500978705</v>
+        <v>0.1007535048703225</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.162230454661263</v>
+        <v>-1.935849089729337</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.673498238544237</v>
+        <v>1.809327057503393</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-7.064197555374829</v>
+        <v>-6.94928345572349</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1438215424936131</v>
+        <v>0.1897871823541486</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.93719745499244</v>
+        <v>-1.710816090060514</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.807538515961828</v>
+        <v>1.943367334920984</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.849563177738422</v>
+        <v>-6.734649078087084</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2343700946024931</v>
+        <v>0.2803357344630286</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.722563077356034</v>
+        <v>-1.496181712424107</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.94101394359799</v>
+        <v>2.076842762557146</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.58296282076407</v>
+        <v>-6.468048721112732</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3222044961760298</v>
+        <v>0.3681701360365648</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.722563077356034</v>
+        <v>-1.496181712424107</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.922208202381785</v>
+        <v>2.058037021340941</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.34253232395921</v>
+        <v>-6.227618224307871</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4201197715228511</v>
+        <v>0.4660854113833865</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.482132580551173</v>
+        <v>-1.255751215619247</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.068209577089579</v>
+        <v>2.204038396048734</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.099741516309765</v>
+        <v>-5.984827416658426</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5211654084174495</v>
+        <v>0.567131048277985</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.482132580551173</v>
+        <v>-1.255751215619247</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.072138890924399</v>
+        <v>2.207967709883555</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.983801666684579</v>
+        <v>-5.868887567033241</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5682199321848636</v>
+        <v>0.614185572045399</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.405310849535049</v>
+        <v>-1.178929484603123</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.118910513451413</v>
+        <v>2.254739332410569</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.741146078261416</v>
+        <v>-5.626231978610077</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6622802387741227</v>
+        <v>0.7082458786346582</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.405310849535049</v>
+        <v>-1.178929484603123</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.115908584671407</v>
+        <v>2.251737403630563</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.521125280224405</v>
+        <v>-5.406211180573067</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.751867594999541</v>
+        <v>0.7978332348600765</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.264091004467069</v>
+        <v>-1.037709639535143</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.202219528722809</v>
+        <v>2.338048347681965</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.321876650319596</v>
+        <v>-5.206962550668258</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.847461229763288</v>
+        <v>0.8934268696238234</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.264091004467069</v>
+        <v>-1.037709639535143</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.218113711524632</v>
+        <v>2.353942530483788</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.162361546800226</v>
+        <v>-5.047447447148888</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9124131156113378</v>
+        <v>0.9583787554718732</v>
       </c>
       <c r="F1931" t="n">
-        <v>-1.104575900947699</v>
+        <v>-0.8781945360157727</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.314968618076556</v>
+        <v>2.450797437035712</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.017689401700489</v>
+        <v>-4.90277530204915</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9803700762126724</v>
+        <v>1.026335716073208</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.9599037558479617</v>
+        <v>-0.7335223909160353</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.411860007697839</v>
+        <v>2.547688826656994</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.077564229058181</v>
+        <v>-4.962650129406843</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9424576366710213</v>
+        <v>0.9884232765315568</v>
       </c>
       <c r="F1933" t="n">
-        <v>-1.019778583205654</v>
+        <v>-0.7933972182737274</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.361972602684649</v>
+        <v>2.497801421643805</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.990764731279173</v>
+        <v>-4.875850631627834</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9995779291051909</v>
+        <v>1.045543568965726</v>
       </c>
       <c r="F1934" t="n">
-        <v>-1.019778583205654</v>
+        <v>-0.7933972182737274</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.384373096007215</v>
+        <v>2.520201914966371</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.993234437740979</v>
+        <v>-4.87832033808964</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9986624478938806</v>
+        <v>1.044628087754416</v>
       </c>
       <c r="F1935" t="n">
-        <v>-1.02224828966746</v>
+        <v>-0.7958669247355337</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.382963673503544</v>
+        <v>2.518792492462699</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.061604624064989</v>
+        <v>-4.946690524413651</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9823212958389784</v>
+        <v>1.028286935699514</v>
       </c>
       <c r="F1936" t="n">
-        <v>-1.012972590631245</v>
+        <v>-0.7865912256993187</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.399536015399975</v>
+        <v>2.53536483435913</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.940188194438512</v>
+        <v>-4.825274094787174</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.02132457632146</v>
+        <v>1.067290216181996</v>
       </c>
       <c r="F1937" t="n">
-        <v>-1.012972590631245</v>
+        <v>-0.7865912256993187</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.389972724031866</v>
+        <v>2.525801542991021</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.971181353767218</v>
+        <v>-4.856267254115879</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8336368776303651</v>
+        <v>0.8796025174909006</v>
       </c>
       <c r="F1938" t="n">
-        <v>-1.012972590631245</v>
+        <v>-0.7865912256993187</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.214682289072253</v>
+        <v>2.350511108031408</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.795707093974748</v>
+        <v>-4.68079299432341</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9083938135391407</v>
+        <v>0.9543594533996762</v>
       </c>
       <c r="F1939" t="n">
-        <v>-1.012972590631245</v>
+        <v>-0.7865912256993187</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.21924952106404</v>
+        <v>2.355078340023196</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.906643346615997</v>
+        <v>-4.791729246964659</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8640307863694388</v>
+        <v>0.909996426229974</v>
       </c>
       <c r="F1940" t="n">
-        <v>-1.012972590631245</v>
+        <v>-0.7865912256993187</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.219260994950838</v>
+        <v>2.355089813909994</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.10966992415923</v>
+        <v>-4.994755824507892</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.785951540572051</v>
+        <v>0.8319171804325864</v>
       </c>
       <c r="F1941" t="n">
-        <v>-1.215999168174479</v>
+        <v>-0.9896178032425521</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.100576433644803</v>
+        <v>2.23640525260396</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.951744325223937</v>
+        <v>-4.836830225572599</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8592941665783005</v>
+        <v>0.905259806438836</v>
       </c>
       <c r="F1942" t="n">
-        <v>-1.215999168174479</v>
+        <v>-0.9896178032425521</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.110748820076936</v>
+        <v>2.246577639036092</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.100065579035066</v>
+        <v>-4.985151479383727</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7949119356277095</v>
+        <v>0.8408775754882447</v>
       </c>
       <c r="F1943" t="n">
-        <v>-1.215999168174479</v>
+        <v>-0.9896178032425521</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.105695090650796</v>
+        <v>2.241523909609952</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.101248663686127</v>
+        <v>-4.986334564034788</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7862144772118107</v>
+        <v>0.8321801170723462</v>
       </c>
       <c r="F1944" t="n">
-        <v>-1.22164221664099</v>
+        <v>-0.9952608517090636</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.094085037015415</v>
+        <v>2.229913855974571</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.978120956692043</v>
+        <v>-4.863206857040705</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8360174330425454</v>
+        <v>0.8819830729030809</v>
       </c>
       <c r="F1945" t="n">
-        <v>-1.22164221664099</v>
+        <v>-0.9952608517090636</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.094636910048516</v>
+        <v>2.230465729007672</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.885310475241184</v>
+        <v>-4.770396375589845</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8024143175142551</v>
+        <v>0.8483799573747903</v>
       </c>
       <c r="F1946" t="n">
-        <v>-1.128831735190131</v>
+        <v>-0.9024503702582043</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.079595890810397</v>
+        <v>2.215424709769553</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.836747423020154</v>
+        <v>-4.721833323368815</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8237130143272677</v>
+        <v>0.8696786541878032</v>
       </c>
       <c r="F1947" t="n">
-        <v>-1.080268682969101</v>
+        <v>-0.8538873180371741</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.110607198067616</v>
+        <v>2.246436017026772</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.724076204783904</v>
+        <v>-4.609162105132565</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8638572101334909</v>
+        <v>0.9098228499940262</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.9675974647328505</v>
+        <v>-0.7412160998009238</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.17328563752109</v>
+        <v>2.309114456480245</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.611699203601231</v>
+        <v>-4.496785103949892</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9142993064372273</v>
+        <v>0.9602649462977626</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.9675974647328505</v>
+        <v>-0.7412160998009238</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.178776933351757</v>
+        <v>2.314605752310912</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.392357698660958</v>
+        <v>3.639181518234836</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.636696816378729</v>
+        <v>2.833060579053746</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.611699203601231</v>
+        <v>-4.496785103949892</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9142993064372273</v>
+        <v>0.9602649462977626</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.9675974647328505</v>
+        <v>-0.7412160998009238</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.629760613365097</v>
+        <v>2.826124376040114</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712295</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349968</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.639181518234836</v>
+        <v>3.639181518234834</v>
       </c>
       <c r="C1950" t="n">
         <v>2.833060579053746</v>

--- a/tame_output/ON/bt/strategyON_20240430.xlsx
+++ b/tame_output/ON/bt/strategyON_20240430.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>443.3%</t>
+          <t>443.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.3%</t>
+          <t>-616.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-124.1%</t>
+          <t>-124.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.2%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-298.1%</t>
+          <t>-303.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.4%</t>
+          <t>-216.7%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -46398,19 +46398,19 @@
         <v>3.639181518234834</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.833060579053746</v>
+        <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.496785103949892</v>
+        <v>-4.552232514955146</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9602649462977626</v>
+        <v>0.9495831836642001</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.7412160998009238</v>
+        <v>-0.7966635108061777</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.826124376040114</v>
+        <v>2.292834507476299</v>
       </c>
     </row>
   </sheetData>
